--- a/data/trans_orig/P79A10_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79A10_2023-Edad-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22336</t>
+          <t>26376</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>89,7%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>66,32%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>29406</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>29406</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>29406</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18821</t>
+          <t>22179</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24619</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>32994</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18751</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11839</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11839</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11839</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>37664</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37664</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37664</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>18724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21843</t>
+          <t>26257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>17036</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>19524</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34235</t>
+          <t>40208</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28869</t>
+          <t>33477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>44007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>827</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>27084</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>27084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>27084</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40770</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40770</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40770</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21823</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26609</t>
+          <t>29022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>24595</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17149</t>
+          <t>21060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>49630</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35892</t>
+          <t>42408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47247</t>
+          <t>54887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>13924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>27168</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>27168</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>27168</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>51931</t>
+          <t>59958</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>51931</t>
+          <t>59958</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>51931</t>
+          <t>59958</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>24616</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>19437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>22084</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>18162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>24809</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41077</t>
+          <t>46701</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>40476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45268</t>
+          <t>51362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>29996</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>29996</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>29996</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>51364</t>
+          <t>57440</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51364</t>
+          <t>57440</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51364</t>
+          <t>57440</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,27 +2440,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>12279</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11995</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15469</t>
+          <t>17254</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21450</t>
+          <t>24481</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>30415</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>381</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>28094</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28094</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28094</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2818,27 +2818,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>27516</t>
+          <t>30928</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>29046</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>31529</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>601</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>601</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>31529</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>31529</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>31529</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>111250</t>
+          <t>127650</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99232</t>
+          <t>111307</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120296</t>
+          <t>138862</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>103497</t>
+          <t>120360</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>108837</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111253</t>
+          <t>128128</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>214748</t>
+          <t>248009</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>196269</t>
+          <t>229941</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>227843</t>
+          <t>261933</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>29957</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>46300</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>16823</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>36114</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>54549</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65591</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
